--- a/results/dataset2_ANN_CPU_model_results.xlsx
+++ b/results/dataset2_ANN_CPU_model_results.xlsx
@@ -7,14 +7,19 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" r:id="rId1"/>
+    <sheet name="Rank_1_Best" sheetId="1" r:id="rId1"/>
+    <sheet name="Rank_2" sheetId="2" r:id="rId2"/>
+    <sheet name="Rank_3" sheetId="3" r:id="rId3"/>
+    <sheet name="Rank_4" sheetId="4" r:id="rId4"/>
+    <sheet name="Rank_5" sheetId="5" r:id="rId5"/>
+    <sheet name="All_Combinations" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="24">
   <si>
     <t>Observation</t>
   </si>
@@ -46,10 +51,10 @@
     <t>alpha</t>
   </si>
   <si>
-    <t>avg_rmse</t>
+    <t>rmse</t>
   </si>
   <si>
-    <t>avg_mae</t>
+    <t>mae</t>
   </si>
   <si>
     <t>r2</t>
@@ -62,6 +67,30 @@
   </si>
   <si>
     <t>0.01</t>
+  </si>
+  <si>
+    <t>0.001</t>
+  </si>
+  <si>
+    <t>(10, 5)</t>
+  </si>
+  <si>
+    <t>(8, 4)</t>
+  </si>
+  <si>
+    <t>logistic</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>RMSE</t>
+  </si>
+  <si>
+    <t>MAE</t>
+  </si>
+  <si>
+    <t>relu</t>
   </si>
 </sst>
 </file>
@@ -440,13 +469,13 @@
         <v>9.07</v>
       </c>
       <c r="C2">
-        <v>9.063750125946207</v>
+        <v>9.06</v>
       </c>
       <c r="D2">
-        <v>0.006249874053793292</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="E2">
-        <v>3.90609256882786E-05</v>
+        <v>9.999999999999574E-05</v>
       </c>
       <c r="H2" t="s">
         <v>7</v>
@@ -463,13 +492,13 @@
         <v>8.970000000000001</v>
       </c>
       <c r="C3">
-        <v>8.960474485072167</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="D3">
-        <v>0.009525514927833711</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="E3">
-        <v>9.073543464038288E-05</v>
+        <v>9.999999999999574E-05</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -486,13 +515,13 @@
         <v>8.720000000000001</v>
       </c>
       <c r="C4">
-        <v>8.730017979766348</v>
+        <v>8.73</v>
       </c>
       <c r="D4">
-        <v>0.01001797976634755</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="E4">
-        <v>0.0001003599185989489</v>
+        <v>9.999999999999574E-05</v>
       </c>
       <c r="H4" t="s">
         <v>9</v>
@@ -509,13 +538,13 @@
         <v>9.24</v>
       </c>
       <c r="C5">
-        <v>9.235632303066268</v>
+        <v>9.24</v>
       </c>
       <c r="D5">
-        <v>0.00436769693373229</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>1.907677650493445E-05</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
         <v>10</v>
@@ -532,13 +561,13 @@
         <v>9.140000000000001</v>
       </c>
       <c r="C6">
-        <v>9.136211571638921</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="D6">
-        <v>0.003788428361080065</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>1.435218944703579E-05</v>
+        <v>0</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
@@ -555,13 +584,13 @@
         <v>8.890000000000001</v>
       </c>
       <c r="C7">
-        <v>8.905084463733584</v>
+        <v>8.91</v>
       </c>
       <c r="D7">
-        <v>0.01508446373358296</v>
+        <v>0.01999999999999957</v>
       </c>
       <c r="E7">
-        <v>0.0002275410461297797</v>
+        <v>0.0003999999999999829</v>
       </c>
       <c r="H7" t="s">
         <v>12</v>
@@ -578,13 +607,13 @@
         <v>10.33</v>
       </c>
       <c r="C8">
-        <v>10.34703427133104</v>
+        <v>10.35</v>
       </c>
       <c r="D8">
-        <v>0.01703427133104007</v>
+        <v>0.01999999999999957</v>
       </c>
       <c r="E8">
-        <v>0.0002901663997794938</v>
+        <v>0.0003999999999999829</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -595,13 +624,13 @@
         <v>10.24</v>
       </c>
       <c r="C9">
-        <v>10.23196396247046</v>
+        <v>10.23</v>
       </c>
       <c r="D9">
-        <v>0.00803603752953741</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="E9">
-        <v>6.457789917613371E-05</v>
+        <v>9.999999999999574E-05</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -612,13 +641,13 @@
         <v>9.99</v>
       </c>
       <c r="C10">
-        <v>10.0112169156</v>
+        <v>10.01</v>
       </c>
       <c r="D10">
-        <v>0.02121691560000194</v>
+        <v>0.01999999999999957</v>
       </c>
       <c r="E10">
-        <v>0.0004501575075776057</v>
+        <v>0.0003999999999999829</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -629,13 +658,13 @@
         <v>7.66</v>
       </c>
       <c r="C11">
-        <v>7.677575330553994</v>
+        <v>7.68</v>
       </c>
       <c r="D11">
-        <v>0.01757533055399385</v>
+        <v>0.01999999999999957</v>
       </c>
       <c r="E11">
-        <v>0.0003088922440821498</v>
+        <v>0.0003999999999999829</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -646,13 +675,13 @@
         <v>7.57</v>
       </c>
       <c r="C12">
-        <v>7.567270293547021</v>
+        <v>7.57</v>
       </c>
       <c r="D12">
-        <v>0.002729706452979208</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>7.45129731943633E-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -663,13 +692,13 @@
         <v>7.32</v>
       </c>
       <c r="C13">
-        <v>7.333070324417985</v>
+        <v>7.33</v>
       </c>
       <c r="D13">
-        <v>0.01307032441798484</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="E13">
-        <v>0.0001708333803913706</v>
+        <v>9.999999999999574E-05</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -680,13 +709,13 @@
         <v>11.53</v>
       </c>
       <c r="C14">
-        <v>11.51563795593463</v>
+        <v>11.52</v>
       </c>
       <c r="D14">
-        <v>0.01436204406537378</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="E14">
-        <v>0.0002062683097357382</v>
+        <v>9.999999999999574E-05</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -697,13 +726,13 @@
         <v>11.43</v>
       </c>
       <c r="C15">
-        <v>11.41567184277539</v>
+        <v>11.42</v>
       </c>
       <c r="D15">
-        <v>0.01432815722461456</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="E15">
-        <v>0.0002052960894532743</v>
+        <v>9.999999999999574E-05</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -714,13 +743,13 @@
         <v>11.18</v>
       </c>
       <c r="C16">
-        <v>11.17544790776093</v>
+        <v>11.18</v>
       </c>
       <c r="D16">
-        <v>0.00455209223906472</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>2.072154375295326E-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -731,13 +760,13 @@
         <v>8.65</v>
       </c>
       <c r="C17">
-        <v>8.645500054404296</v>
+        <v>8.65</v>
       </c>
       <c r="D17">
-        <v>0.004499945595703991</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>2.024951036429575E-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -748,13 +777,13 @@
         <v>8.550000000000001</v>
       </c>
       <c r="C18">
-        <v>8.551838205933777</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="D18">
-        <v>0.001838205933776038</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>3.379001054969436E-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -765,13 +794,13 @@
         <v>8.31</v>
       </c>
       <c r="C19">
-        <v>8.312835677085271</v>
+        <v>8.31</v>
       </c>
       <c r="D19">
-        <v>0.00283567708527066</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>8.041064531929108E-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -782,13 +811,13 @@
         <v>9.890000000000001</v>
       </c>
       <c r="C20">
-        <v>9.888500019661986</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="D20">
-        <v>0.00149998033801424</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>2.249941014429312E-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -799,13 +828,13 @@
         <v>9.789999999999999</v>
       </c>
       <c r="C21">
-        <v>9.78914119108131</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="D21">
-        <v>0.000858808918689391</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>7.375527588204411E-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -816,13 +845,13 @@
         <v>9.550000000000001</v>
       </c>
       <c r="C22">
-        <v>9.544895890714555</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="D22">
-        <v>0.005104109285445801</v>
+        <v>0.01000000000000156</v>
       </c>
       <c r="E22">
-        <v>2.605193159777405E-05</v>
+        <v>0.0001000000000000313</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -833,13 +862,13 @@
         <v>9.779999999999999</v>
       </c>
       <c r="C23">
-        <v>9.728678341143471</v>
+        <v>9.73</v>
       </c>
       <c r="D23">
-        <v>0.05132165885652817</v>
+        <v>0.04999999999999893</v>
       </c>
       <c r="E23">
-        <v>0.002633912667785857</v>
+        <v>0.002499999999999893</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -850,13 +879,13 @@
         <v>9.69</v>
       </c>
       <c r="C24">
-        <v>9.674027758522159</v>
+        <v>9.67</v>
       </c>
       <c r="D24">
-        <v>0.01597224147784004</v>
+        <v>0.01999999999999957</v>
       </c>
       <c r="E24">
-        <v>0.0002551124978264339</v>
+        <v>0.0003999999999999829</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -867,13 +896,13 @@
         <v>9.44</v>
       </c>
       <c r="C25">
-        <v>9.437542109899418</v>
+        <v>9.44</v>
       </c>
       <c r="D25">
-        <v>0.002457890100581395</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>6.041223746536019E-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -884,13 +913,13 @@
         <v>7.19</v>
       </c>
       <c r="C26">
-        <v>7.195629789519812</v>
+        <v>7.2</v>
       </c>
       <c r="D26">
-        <v>0.005629789519812078</v>
+        <v>0.009999999999999787</v>
       </c>
       <c r="E26">
-        <v>3.169453003738591E-05</v>
+        <v>9.999999999999574E-05</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -901,13 +930,13 @@
         <v>7.09</v>
       </c>
       <c r="C27">
-        <v>7.090425354456258</v>
+        <v>7.09</v>
       </c>
       <c r="D27">
-        <v>0.0004253544562580203</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>1.809264134585561E-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -918,13 +947,3074 @@
         <v>6.84</v>
       </c>
       <c r="C28">
-        <v>6.855526390730101</v>
+        <v>6.86</v>
       </c>
       <c r="D28">
-        <v>0.01552639073010109</v>
+        <v>0.02000000000000046</v>
       </c>
       <c r="E28">
-        <v>0.0002410688091037691</v>
+        <v>0.0004000000000000185</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="5" width="18.7109375" customWidth="1"/>
+    <col min="8" max="9" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>9.07</v>
+      </c>
+      <c r="C2">
+        <v>9.06</v>
+      </c>
+      <c r="D2">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="E2">
+        <v>9.999999999999574E-05</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="C3">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="C4">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="D4">
+        <v>0.02000000000000135</v>
+      </c>
+      <c r="E4">
+        <v>0.000400000000000054</v>
+      </c>
+      <c r="H4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>9.24</v>
+      </c>
+      <c r="C5">
+        <v>9.24</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>0.0173114368051857</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="C6">
+        <v>9.15</v>
+      </c>
+      <c r="D6">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="E6">
+        <v>9.999999999999574E-05</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>0.01296867478511019</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="C7">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>0.9998128019190947</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>10.33</v>
+      </c>
+      <c r="C8">
+        <v>10.35</v>
+      </c>
+      <c r="D8">
+        <v>0.01999999999999957</v>
+      </c>
+      <c r="E8">
+        <v>0.0003999999999999829</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>10.24</v>
+      </c>
+      <c r="C9">
+        <v>10.23</v>
+      </c>
+      <c r="D9">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="E9">
+        <v>9.999999999999574E-05</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>9.99</v>
+      </c>
+      <c r="C10">
+        <v>9.98</v>
+      </c>
+      <c r="D10">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="E10">
+        <v>9.999999999999574E-05</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>7.66</v>
+      </c>
+      <c r="C11">
+        <v>7.7</v>
+      </c>
+      <c r="D11">
+        <v>0.04000000000000004</v>
+      </c>
+      <c r="E11">
+        <v>0.001600000000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>7.57</v>
+      </c>
+      <c r="C12">
+        <v>7.57</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>7.32</v>
+      </c>
+      <c r="C13">
+        <v>7.32</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>11.53</v>
+      </c>
+      <c r="C14">
+        <v>11.49</v>
+      </c>
+      <c r="D14">
+        <v>0.03999999999999915</v>
+      </c>
+      <c r="E14">
+        <v>0.001599999999999932</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>11.43</v>
+      </c>
+      <c r="C15">
+        <v>11.43</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>11.18</v>
+      </c>
+      <c r="C16">
+        <v>11.19</v>
+      </c>
+      <c r="D16">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="E16">
+        <v>9.999999999999574E-05</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>8.65</v>
+      </c>
+      <c r="C17">
+        <v>8.66</v>
+      </c>
+      <c r="D17">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="E17">
+        <v>9.999999999999574E-05</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="C18">
+        <v>8.56</v>
+      </c>
+      <c r="D18">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="E18">
+        <v>9.999999999999574E-05</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>8.31</v>
+      </c>
+      <c r="C19">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="D19">
+        <v>0.02000000000000135</v>
+      </c>
+      <c r="E19">
+        <v>0.000400000000000054</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="C20">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="D20">
+        <v>0.02000000000000135</v>
+      </c>
+      <c r="E20">
+        <v>0.000400000000000054</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="C21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D21">
+        <v>0.01000000000000156</v>
+      </c>
+      <c r="E21">
+        <v>0.0001000000000000313</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="C22">
+        <v>9.51</v>
+      </c>
+      <c r="D22">
+        <v>0.04000000000000092</v>
+      </c>
+      <c r="E22">
+        <v>0.001600000000000074</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="C23">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="D23">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="E23">
+        <v>9.999999999999574E-05</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>9.69</v>
+      </c>
+      <c r="C24">
+        <v>9.68</v>
+      </c>
+      <c r="D24">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="E24">
+        <v>9.999999999999574E-05</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>9.44</v>
+      </c>
+      <c r="C25">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="D25">
+        <v>0.03000000000000114</v>
+      </c>
+      <c r="E25">
+        <v>0.0009000000000000682</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>7.19</v>
+      </c>
+      <c r="C26">
+        <v>7.17</v>
+      </c>
+      <c r="D26">
+        <v>0.02000000000000046</v>
+      </c>
+      <c r="E26">
+        <v>0.0004000000000000185</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>7.09</v>
+      </c>
+      <c r="C27">
+        <v>7.09</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>6.84</v>
+      </c>
+      <c r="C28">
+        <v>6.85</v>
+      </c>
+      <c r="D28">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="E28">
+        <v>9.999999999999574E-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="5" width="18.7109375" customWidth="1"/>
+    <col min="8" max="9" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>9.07</v>
+      </c>
+      <c r="C2">
+        <v>9.07</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="C3">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="D3">
+        <v>0.02000000000000135</v>
+      </c>
+      <c r="E3">
+        <v>0.000400000000000054</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="C4">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>9.24</v>
+      </c>
+      <c r="C5">
+        <v>9.23</v>
+      </c>
+      <c r="D5">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="E5">
+        <v>9.999999999999574E-05</v>
+      </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>0.03983563140840875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="C6">
+        <v>9.15</v>
+      </c>
+      <c r="D6">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="E6">
+        <v>9.999999999999574E-05</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>0.02965657745370917</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="C7">
+        <v>8.91</v>
+      </c>
+      <c r="D7">
+        <v>0.01999999999999957</v>
+      </c>
+      <c r="E7">
+        <v>0.0003999999999999829</v>
+      </c>
+      <c r="H7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>0.9990087605608255</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>10.33</v>
+      </c>
+      <c r="C8">
+        <v>10.43</v>
+      </c>
+      <c r="D8">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="E8">
+        <v>0.009999999999999929</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>10.24</v>
+      </c>
+      <c r="C9">
+        <v>10.25</v>
+      </c>
+      <c r="D9">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="E9">
+        <v>9.999999999999574E-05</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>9.99</v>
+      </c>
+      <c r="C10">
+        <v>10.02</v>
+      </c>
+      <c r="D10">
+        <v>0.02999999999999936</v>
+      </c>
+      <c r="E10">
+        <v>0.0008999999999999616</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>7.66</v>
+      </c>
+      <c r="C11">
+        <v>7.72</v>
+      </c>
+      <c r="D11">
+        <v>0.05999999999999961</v>
+      </c>
+      <c r="E11">
+        <v>0.003599999999999953</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>7.57</v>
+      </c>
+      <c r="C12">
+        <v>7.53</v>
+      </c>
+      <c r="D12">
+        <v>0.04000000000000004</v>
+      </c>
+      <c r="E12">
+        <v>0.001600000000000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>7.32</v>
+      </c>
+      <c r="C13">
+        <v>7.37</v>
+      </c>
+      <c r="D13">
+        <v>0.04999999999999982</v>
+      </c>
+      <c r="E13">
+        <v>0.002499999999999982</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>11.53</v>
+      </c>
+      <c r="C14">
+        <v>11.49</v>
+      </c>
+      <c r="D14">
+        <v>0.03999999999999915</v>
+      </c>
+      <c r="E14">
+        <v>0.001599999999999932</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>11.43</v>
+      </c>
+      <c r="C15">
+        <v>11.43</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>11.18</v>
+      </c>
+      <c r="C16">
+        <v>11.23</v>
+      </c>
+      <c r="D16">
+        <v>0.05000000000000071</v>
+      </c>
+      <c r="E16">
+        <v>0.002500000000000071</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>8.65</v>
+      </c>
+      <c r="C17">
+        <v>8.65</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="C18">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>8.31</v>
+      </c>
+      <c r="C19">
+        <v>8.27</v>
+      </c>
+      <c r="D19">
+        <v>0.04000000000000092</v>
+      </c>
+      <c r="E19">
+        <v>0.001600000000000074</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="C20">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="D20">
+        <v>0.05999999999999872</v>
+      </c>
+      <c r="E20">
+        <v>0.003599999999999846</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="C21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D21">
+        <v>0.01000000000000156</v>
+      </c>
+      <c r="E21">
+        <v>0.0001000000000000313</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="C22">
+        <v>9.52</v>
+      </c>
+      <c r="D22">
+        <v>0.03000000000000114</v>
+      </c>
+      <c r="E22">
+        <v>0.0009000000000000682</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="C23">
+        <v>9.77</v>
+      </c>
+      <c r="D23">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="E23">
+        <v>9.999999999999574E-05</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>9.69</v>
+      </c>
+      <c r="C24">
+        <v>9.69</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>9.44</v>
+      </c>
+      <c r="C25">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="D25">
+        <v>0.02000000000000135</v>
+      </c>
+      <c r="E25">
+        <v>0.000400000000000054</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>7.19</v>
+      </c>
+      <c r="C26">
+        <v>7.27</v>
+      </c>
+      <c r="D26">
+        <v>0.07999999999999918</v>
+      </c>
+      <c r="E26">
+        <v>0.006399999999999869</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>7.09</v>
+      </c>
+      <c r="C27">
+        <v>7.07</v>
+      </c>
+      <c r="D27">
+        <v>0.01999999999999957</v>
+      </c>
+      <c r="E27">
+        <v>0.0003999999999999829</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>6.84</v>
+      </c>
+      <c r="C28">
+        <v>6.92</v>
+      </c>
+      <c r="D28">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="E28">
+        <v>0.006400000000000012</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="5" width="18.7109375" customWidth="1"/>
+    <col min="8" max="9" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>9.07</v>
+      </c>
+      <c r="C2">
+        <v>8.98</v>
+      </c>
+      <c r="D2">
+        <v>0.08999999999999986</v>
+      </c>
+      <c r="E2">
+        <v>0.008099999999999975</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="C3">
+        <v>8.99</v>
+      </c>
+      <c r="D3">
+        <v>0.01999999999999957</v>
+      </c>
+      <c r="E3">
+        <v>0.0003999999999999829</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="C4">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="D4">
+        <v>0.02000000000000135</v>
+      </c>
+      <c r="E4">
+        <v>0.000400000000000054</v>
+      </c>
+      <c r="H4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>9.24</v>
+      </c>
+      <c r="C5">
+        <v>9.19</v>
+      </c>
+      <c r="D5">
+        <v>0.05000000000000071</v>
+      </c>
+      <c r="E5">
+        <v>0.002500000000000071</v>
+      </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>0.04573058975366982</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="C6">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="D6">
+        <v>0.02000000000000135</v>
+      </c>
+      <c r="E6">
+        <v>0.000400000000000054</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>0.03486586386576107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="C7">
+        <v>8.84</v>
+      </c>
+      <c r="D7">
+        <v>0.05000000000000071</v>
+      </c>
+      <c r="E7">
+        <v>0.002500000000000071</v>
+      </c>
+      <c r="H7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>0.9986936824330463</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>10.33</v>
+      </c>
+      <c r="C8">
+        <v>10.33</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>10.24</v>
+      </c>
+      <c r="C9">
+        <v>10.26</v>
+      </c>
+      <c r="D9">
+        <v>0.01999999999999957</v>
+      </c>
+      <c r="E9">
+        <v>0.0003999999999999829</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>9.99</v>
+      </c>
+      <c r="C10">
+        <v>9.9</v>
+      </c>
+      <c r="D10">
+        <v>0.08999999999999986</v>
+      </c>
+      <c r="E10">
+        <v>0.008099999999999975</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>7.66</v>
+      </c>
+      <c r="C11">
+        <v>7.71</v>
+      </c>
+      <c r="D11">
+        <v>0.04999999999999982</v>
+      </c>
+      <c r="E11">
+        <v>0.002499999999999982</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>7.57</v>
+      </c>
+      <c r="C12">
+        <v>7.55</v>
+      </c>
+      <c r="D12">
+        <v>0.02000000000000046</v>
+      </c>
+      <c r="E12">
+        <v>0.0004000000000000185</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>7.32</v>
+      </c>
+      <c r="C13">
+        <v>7.44</v>
+      </c>
+      <c r="D13">
+        <v>0.1200000000000001</v>
+      </c>
+      <c r="E13">
+        <v>0.01440000000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>11.53</v>
+      </c>
+      <c r="C14">
+        <v>11.5</v>
+      </c>
+      <c r="D14">
+        <v>0.02999999999999936</v>
+      </c>
+      <c r="E14">
+        <v>0.0008999999999999616</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>11.43</v>
+      </c>
+      <c r="C15">
+        <v>11.43</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>11.18</v>
+      </c>
+      <c r="C16">
+        <v>11.23</v>
+      </c>
+      <c r="D16">
+        <v>0.05000000000000071</v>
+      </c>
+      <c r="E16">
+        <v>0.002500000000000071</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>8.65</v>
+      </c>
+      <c r="C17">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="D17">
+        <v>0.01999999999999957</v>
+      </c>
+      <c r="E17">
+        <v>0.0003999999999999829</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="C18">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="D18">
+        <v>0.01000000000000156</v>
+      </c>
+      <c r="E18">
+        <v>0.0001000000000000313</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>8.31</v>
+      </c>
+      <c r="C19">
+        <v>8.34</v>
+      </c>
+      <c r="D19">
+        <v>0.02999999999999936</v>
+      </c>
+      <c r="E19">
+        <v>0.0008999999999999616</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="C20">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="D20">
+        <v>0.02000000000000135</v>
+      </c>
+      <c r="E20">
+        <v>0.000400000000000054</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="C21">
+        <v>9.83</v>
+      </c>
+      <c r="D21">
+        <v>0.04000000000000092</v>
+      </c>
+      <c r="E21">
+        <v>0.001600000000000074</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="C22">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="D22">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="E22">
+        <v>0.006400000000000012</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="C23">
+        <v>9.74</v>
+      </c>
+      <c r="D23">
+        <v>0.03999999999999915</v>
+      </c>
+      <c r="E23">
+        <v>0.001599999999999932</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>9.69</v>
+      </c>
+      <c r="C24">
+        <v>9.69</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>9.44</v>
+      </c>
+      <c r="C25">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="D25">
+        <v>0.02000000000000135</v>
+      </c>
+      <c r="E25">
+        <v>0.000400000000000054</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>7.19</v>
+      </c>
+      <c r="C26">
+        <v>7.23</v>
+      </c>
+      <c r="D26">
+        <v>0.04000000000000004</v>
+      </c>
+      <c r="E26">
+        <v>0.001600000000000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>7.09</v>
+      </c>
+      <c r="C27">
+        <v>7.08</v>
+      </c>
+      <c r="D27">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="E27">
+        <v>9.999999999999574E-05</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>6.84</v>
+      </c>
+      <c r="C28">
+        <v>6.85</v>
+      </c>
+      <c r="D28">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="E28">
+        <v>9.999999999999574E-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="5" width="18.7109375" customWidth="1"/>
+    <col min="8" max="9" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>9.07</v>
+      </c>
+      <c r="C2">
+        <v>9.09</v>
+      </c>
+      <c r="D2">
+        <v>0.01999999999999957</v>
+      </c>
+      <c r="E2">
+        <v>0.0003999999999999829</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="C3">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="D3">
+        <v>0.02000000000000135</v>
+      </c>
+      <c r="E3">
+        <v>0.000400000000000054</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="C4">
+        <v>8.73</v>
+      </c>
+      <c r="D4">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="E4">
+        <v>9.999999999999574E-05</v>
+      </c>
+      <c r="H4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>9.24</v>
+      </c>
+      <c r="C5">
+        <v>9.27</v>
+      </c>
+      <c r="D5">
+        <v>0.02999999999999936</v>
+      </c>
+      <c r="E5">
+        <v>0.0008999999999999616</v>
+      </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>0.04580694418219362</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="C6">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="D6">
+        <v>0.02000000000000135</v>
+      </c>
+      <c r="E6">
+        <v>0.000400000000000054</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>0.03351571075210094</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="C7">
+        <v>8.9</v>
+      </c>
+      <c r="D7">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="E7">
+        <v>9.999999999999574E-05</v>
+      </c>
+      <c r="H7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>0.9986893165851414</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>10.33</v>
+      </c>
+      <c r="C8">
+        <v>10.42</v>
+      </c>
+      <c r="D8">
+        <v>0.08999999999999986</v>
+      </c>
+      <c r="E8">
+        <v>0.008099999999999975</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>10.24</v>
+      </c>
+      <c r="C9">
+        <v>10.22</v>
+      </c>
+      <c r="D9">
+        <v>0.01999999999999957</v>
+      </c>
+      <c r="E9">
+        <v>0.0003999999999999829</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>9.99</v>
+      </c>
+      <c r="C10">
+        <v>10.01</v>
+      </c>
+      <c r="D10">
+        <v>0.01999999999999957</v>
+      </c>
+      <c r="E10">
+        <v>0.0003999999999999829</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>7.66</v>
+      </c>
+      <c r="C11">
+        <v>7.71</v>
+      </c>
+      <c r="D11">
+        <v>0.04999999999999982</v>
+      </c>
+      <c r="E11">
+        <v>0.002499999999999982</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>7.57</v>
+      </c>
+      <c r="C12">
+        <v>7.57</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>7.32</v>
+      </c>
+      <c r="C13">
+        <v>7.45</v>
+      </c>
+      <c r="D13">
+        <v>0.1299999999999999</v>
+      </c>
+      <c r="E13">
+        <v>0.01689999999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>11.53</v>
+      </c>
+      <c r="C14">
+        <v>11.48</v>
+      </c>
+      <c r="D14">
+        <v>0.04999999999999893</v>
+      </c>
+      <c r="E14">
+        <v>0.002499999999999893</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>11.43</v>
+      </c>
+      <c r="C15">
+        <v>11.37</v>
+      </c>
+      <c r="D15">
+        <v>0.0600000000000005</v>
+      </c>
+      <c r="E15">
+        <v>0.00360000000000006</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>11.18</v>
+      </c>
+      <c r="C16">
+        <v>11.18</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>8.65</v>
+      </c>
+      <c r="C17">
+        <v>8.68</v>
+      </c>
+      <c r="D17">
+        <v>0.02999999999999936</v>
+      </c>
+      <c r="E17">
+        <v>0.0008999999999999616</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="C18">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="D18">
+        <v>0.02000000000000135</v>
+      </c>
+      <c r="E18">
+        <v>0.000400000000000054</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>8.31</v>
+      </c>
+      <c r="C19">
+        <v>8.31</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="C20">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="D20">
+        <v>0.05999999999999872</v>
+      </c>
+      <c r="E20">
+        <v>0.003599999999999846</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="C21">
+        <v>9.73</v>
+      </c>
+      <c r="D21">
+        <v>0.05999999999999872</v>
+      </c>
+      <c r="E21">
+        <v>0.003599999999999846</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="C22">
+        <v>9.52</v>
+      </c>
+      <c r="D22">
+        <v>0.03000000000000114</v>
+      </c>
+      <c r="E22">
+        <v>0.0009000000000000682</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="C23">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>9.69</v>
+      </c>
+      <c r="C24">
+        <v>9.65</v>
+      </c>
+      <c r="D24">
+        <v>0.03999999999999915</v>
+      </c>
+      <c r="E24">
+        <v>0.001599999999999932</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>9.44</v>
+      </c>
+      <c r="C25">
+        <v>9.44</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>7.19</v>
+      </c>
+      <c r="C26">
+        <v>7.21</v>
+      </c>
+      <c r="D26">
+        <v>0.01999999999999957</v>
+      </c>
+      <c r="E26">
+        <v>0.0003999999999999829</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>7.09</v>
+      </c>
+      <c r="C27">
+        <v>7.07</v>
+      </c>
+      <c r="D27">
+        <v>0.01999999999999957</v>
+      </c>
+      <c r="E27">
+        <v>0.0003999999999999829</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>6.84</v>
+      </c>
+      <c r="C28">
+        <v>6.92</v>
+      </c>
+      <c r="D28">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="E28">
+        <v>0.006400000000000012</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F46"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="6" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>0.01</v>
+      </c>
+      <c r="D2">
+        <v>0.9998740476378292</v>
+      </c>
+      <c r="E2">
+        <v>0.01419990951785619</v>
+      </c>
+      <c r="F2">
+        <v>0.009996625536628933</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <v>0.001</v>
+      </c>
+      <c r="D3">
+        <v>0.9998128019190947</v>
+      </c>
+      <c r="E3">
+        <v>0.0173114368051857</v>
+      </c>
+      <c r="F3">
+        <v>0.01296867478511019</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>0.01</v>
+      </c>
+      <c r="D4">
+        <v>0.9990087605608255</v>
+      </c>
+      <c r="E4">
+        <v>0.03983563140840875</v>
+      </c>
+      <c r="F4">
+        <v>0.02965657745370917</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5">
+        <v>0.001</v>
+      </c>
+      <c r="D5">
+        <v>0.9986936824330463</v>
+      </c>
+      <c r="E5">
+        <v>0.04573058975366982</v>
+      </c>
+      <c r="F5">
+        <v>0.03486586386576107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6">
+        <v>0.01</v>
+      </c>
+      <c r="D6">
+        <v>0.9986893165851414</v>
+      </c>
+      <c r="E6">
+        <v>0.04580694418219362</v>
+      </c>
+      <c r="F6">
+        <v>0.03351571075210094</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>0.001</v>
+      </c>
+      <c r="D7">
+        <v>0.9986694871947592</v>
+      </c>
+      <c r="E7">
+        <v>0.04615215111578969</v>
+      </c>
+      <c r="F7">
+        <v>0.02683747510206394</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8">
+        <v>0.01</v>
+      </c>
+      <c r="D8">
+        <v>0.9986266346393943</v>
+      </c>
+      <c r="E8">
+        <v>0.04688948505186386</v>
+      </c>
+      <c r="F8">
+        <v>0.03465595224986337</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>0.001</v>
+      </c>
+      <c r="D9">
+        <v>0.9982939762279739</v>
+      </c>
+      <c r="E9">
+        <v>0.05226066814554303</v>
+      </c>
+      <c r="F9">
+        <v>0.03974509423974745</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10">
+        <v>0.01</v>
+      </c>
+      <c r="D10">
+        <v>0.9982667577244222</v>
+      </c>
+      <c r="E10">
+        <v>0.05267591101088784</v>
+      </c>
+      <c r="F10">
+        <v>0.03724328292522854</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11">
+        <v>0.1</v>
+      </c>
+      <c r="D11">
+        <v>0.9977440921890663</v>
+      </c>
+      <c r="E11">
+        <v>0.06009565770680979</v>
+      </c>
+      <c r="F11">
+        <v>0.045077793114763</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12">
+        <v>0.001</v>
+      </c>
+      <c r="D12">
+        <v>0.9974315494691606</v>
+      </c>
+      <c r="E12">
+        <v>0.06412361845957301</v>
+      </c>
+      <c r="F12">
+        <v>0.04326917377119745</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13">
+        <v>0.01</v>
+      </c>
+      <c r="D13">
+        <v>0.9971343489086919</v>
+      </c>
+      <c r="E13">
+        <v>0.06773202724460121</v>
+      </c>
+      <c r="F13">
+        <v>0.03948955952846661</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14">
+        <v>0.01</v>
+      </c>
+      <c r="D14">
+        <v>0.996098610711061</v>
+      </c>
+      <c r="E14">
+        <v>0.07903001461819756</v>
+      </c>
+      <c r="F14">
+        <v>0.0600876988909808</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15">
+        <v>0.1</v>
+      </c>
+      <c r="D15">
+        <v>0.9958820597149857</v>
+      </c>
+      <c r="E15">
+        <v>0.08119372023228184</v>
+      </c>
+      <c r="F15">
+        <v>0.05751245737252301</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16">
+        <v>0.01</v>
+      </c>
+      <c r="D16">
+        <v>0.9953467303675642</v>
+      </c>
+      <c r="E16">
+        <v>0.086310081715942</v>
+      </c>
+      <c r="F16">
+        <v>0.06776464458594118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>0.1</v>
+      </c>
+      <c r="D17">
+        <v>0.9950340204539226</v>
+      </c>
+      <c r="E17">
+        <v>0.08916304299309656</v>
+      </c>
+      <c r="F17">
+        <v>0.07684238850022765</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18">
+        <v>0.1</v>
+      </c>
+      <c r="D18">
+        <v>0.9948012027248543</v>
+      </c>
+      <c r="E18">
+        <v>0.0912291986218028</v>
+      </c>
+      <c r="F18">
+        <v>0.07708712420548249</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19">
+        <v>0.3</v>
+      </c>
+      <c r="D19">
+        <v>0.994694777667553</v>
+      </c>
+      <c r="E19">
+        <v>0.09215824870074921</v>
+      </c>
+      <c r="F19">
+        <v>0.07331293860755875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20">
+        <v>0.1</v>
+      </c>
+      <c r="D20">
+        <v>0.9943090340877565</v>
+      </c>
+      <c r="E20">
+        <v>0.09544988528031058</v>
+      </c>
+      <c r="F20">
+        <v>0.06851081432771497</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21">
+        <v>0.001</v>
+      </c>
+      <c r="D21">
+        <v>0.9942138770399999</v>
+      </c>
+      <c r="E21">
+        <v>0.09624457252063967</v>
+      </c>
+      <c r="F21">
+        <v>0.076850335224556</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22">
+        <v>0.001</v>
+      </c>
+      <c r="D22">
+        <v>0.9928363964240429</v>
+      </c>
+      <c r="E22">
+        <v>0.1070898205713226</v>
+      </c>
+      <c r="F22">
+        <v>0.07502115340330878</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23">
+        <v>0.001</v>
+      </c>
+      <c r="D23">
+        <v>0.9919470185243341</v>
+      </c>
+      <c r="E23">
+        <v>0.1135431055750944</v>
+      </c>
+      <c r="F23">
+        <v>0.07547442964028603</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24">
+        <v>0.3</v>
+      </c>
+      <c r="D24">
+        <v>0.9887885980466377</v>
+      </c>
+      <c r="E24">
+        <v>0.133971487756524</v>
+      </c>
+      <c r="F24">
+        <v>0.104509419150829</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25">
+        <v>0.3</v>
+      </c>
+      <c r="D25">
+        <v>0.9879913215007015</v>
+      </c>
+      <c r="E25">
+        <v>0.1386532416256612</v>
+      </c>
+      <c r="F25">
+        <v>0.1056595567334491</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26">
+        <v>0.5</v>
+      </c>
+      <c r="D26">
+        <v>0.9878095500822582</v>
+      </c>
+      <c r="E26">
+        <v>0.1396986746571842</v>
+      </c>
+      <c r="F26">
+        <v>0.1087300816858155</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27">
+        <v>0.3</v>
+      </c>
+      <c r="D27">
+        <v>0.9834959868472068</v>
+      </c>
+      <c r="E27">
+        <v>0.1625463415245985</v>
+      </c>
+      <c r="F27">
+        <v>0.1297163311323941</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28">
+        <v>0.3</v>
+      </c>
+      <c r="D28">
+        <v>0.9801834103792629</v>
+      </c>
+      <c r="E28">
+        <v>0.1781135158694137</v>
+      </c>
+      <c r="F28">
+        <v>0.130311294188633</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29">
+        <v>0.1</v>
+      </c>
+      <c r="D29">
+        <v>0.9790554172974714</v>
+      </c>
+      <c r="E29">
+        <v>0.1831126191458155</v>
+      </c>
+      <c r="F29">
+        <v>0.1376730128014582</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30">
+        <v>0.1</v>
+      </c>
+      <c r="D30">
+        <v>0.9775833188620209</v>
+      </c>
+      <c r="E30">
+        <v>0.1894384256391248</v>
+      </c>
+      <c r="F30">
+        <v>0.1507012910561114</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31">
+        <v>0.1</v>
+      </c>
+      <c r="D31">
+        <v>0.9749403768518595</v>
+      </c>
+      <c r="E31">
+        <v>0.2002948055640405</v>
+      </c>
+      <c r="F31">
+        <v>0.1550439123990679</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32">
+        <v>0.5</v>
+      </c>
+      <c r="D32">
+        <v>0.9748665029982038</v>
+      </c>
+      <c r="E32">
+        <v>0.2005898151963983</v>
+      </c>
+      <c r="F32">
+        <v>0.156702908099592</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33">
+        <v>0.5</v>
+      </c>
+      <c r="D33">
+        <v>0.9607295335145913</v>
+      </c>
+      <c r="E33">
+        <v>0.2507352814697409</v>
+      </c>
+      <c r="F33">
+        <v>0.1920154069290896</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34">
+        <v>0.5</v>
+      </c>
+      <c r="D34">
+        <v>0.929691774442351</v>
+      </c>
+      <c r="E34">
+        <v>0.3354945636688049</v>
+      </c>
+      <c r="F34">
+        <v>0.2243102955332195</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35">
+        <v>0.5</v>
+      </c>
+      <c r="D35">
+        <v>0.9077078141374264</v>
+      </c>
+      <c r="E35">
+        <v>0.3843836307248614</v>
+      </c>
+      <c r="F35">
+        <v>0.2455852205584235</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36">
+        <v>0.3</v>
+      </c>
+      <c r="D36">
+        <v>0.847859281566518</v>
+      </c>
+      <c r="E36">
+        <v>0.4935204463104573</v>
+      </c>
+      <c r="F36">
+        <v>0.3699808514752871</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37">
+        <v>0.3</v>
+      </c>
+      <c r="D37">
+        <v>0.8402473345729748</v>
+      </c>
+      <c r="E37">
+        <v>0.5057157448796749</v>
+      </c>
+      <c r="F37">
+        <v>0.3793705001293695</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38">
+        <v>0.3</v>
+      </c>
+      <c r="D38">
+        <v>0.802674171616055</v>
+      </c>
+      <c r="E38">
+        <v>0.562049267249865</v>
+      </c>
+      <c r="F38">
+        <v>0.4543577830005471</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39">
+        <v>0.5</v>
+      </c>
+      <c r="D39">
+        <v>0.7470976812406513</v>
+      </c>
+      <c r="E39">
+        <v>0.6362954595628785</v>
+      </c>
+      <c r="F39">
+        <v>0.4894113321503536</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40">
+        <v>0.3</v>
+      </c>
+      <c r="D40">
+        <v>0.7469664210330218</v>
+      </c>
+      <c r="E40">
+        <v>0.6364605617261941</v>
+      </c>
+      <c r="F40">
+        <v>0.4825665233284936</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41">
+        <v>0.1</v>
+      </c>
+      <c r="D41">
+        <v>0.7410733177826321</v>
+      </c>
+      <c r="E41">
+        <v>0.6438294256779989</v>
+      </c>
+      <c r="F41">
+        <v>0.4650947469851175</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" t="s">
+        <v>13</v>
+      </c>
+      <c r="B42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42">
+        <v>0.01</v>
+      </c>
+      <c r="D42">
+        <v>0.7353119927975595</v>
+      </c>
+      <c r="E42">
+        <v>0.6509528769217118</v>
+      </c>
+      <c r="F42">
+        <v>0.4680216244949879</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43">
+        <v>0.001</v>
+      </c>
+      <c r="D43">
+        <v>0.7348525599453735</v>
+      </c>
+      <c r="E43">
+        <v>0.6515175785019908</v>
+      </c>
+      <c r="F43">
+        <v>0.4649293579857346</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44">
+        <v>0.5</v>
+      </c>
+      <c r="D44">
+        <v>0.5963880588506598</v>
+      </c>
+      <c r="E44">
+        <v>0.8038303911855553</v>
+      </c>
+      <c r="F44">
+        <v>0.6213770181920134</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45">
+        <v>0.5</v>
+      </c>
+      <c r="D45">
+        <v>0.3712433680005015</v>
+      </c>
+      <c r="E45">
+        <v>1.003283588226336</v>
+      </c>
+      <c r="F45">
+        <v>0.7465312001359479</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" t="s">
+        <v>17</v>
+      </c>
+      <c r="B46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46">
+        <v>0.5</v>
+      </c>
+      <c r="D46">
+        <v>0.3700663464625333</v>
+      </c>
+      <c r="E46">
+        <v>1.004222213919417</v>
+      </c>
+      <c r="F46">
+        <v>0.7510368500991078</v>
       </c>
     </row>
   </sheetData>

--- a/results/dataset2_ANN_CPU_model_results.xlsx
+++ b/results/dataset2_ANN_CPU_model_results.xlsx
@@ -1,25 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Rank_1_Best" sheetId="1" r:id="rId1"/>
-    <sheet name="Rank_2" sheetId="2" r:id="rId2"/>
-    <sheet name="Rank_3" sheetId="3" r:id="rId3"/>
-    <sheet name="Rank_4" sheetId="4" r:id="rId4"/>
-    <sheet name="Rank_5" sheetId="5" r:id="rId5"/>
-    <sheet name="All_Combinations" sheetId="6" r:id="rId6"/>
+    <sheet name="Rank_1_Best" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rank_2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Rank_3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Rank_4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Rank_5" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="All_Combinations" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr fullCalcOnLoad="1"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Observation</t>
   </si>
@@ -45,10 +47,19 @@
     <t>hidden_layers</t>
   </si>
   <si>
+    <t>(5,)</t>
+  </si>
+  <si>
     <t>activation</t>
   </si>
   <si>
+    <t>tanh</t>
+  </si>
+  <si>
     <t>alpha</t>
+  </si>
+  <si>
+    <t>0.01</t>
   </si>
   <si>
     <t>rmse</t>
@@ -60,22 +71,13 @@
     <t>r2</t>
   </si>
   <si>
-    <t>(5,)</t>
-  </si>
-  <si>
-    <t>tanh</t>
-  </si>
-  <si>
-    <t>0.01</t>
-  </si>
-  <si>
     <t>0.001</t>
   </si>
   <si>
-    <t>(10, 5)</t>
+    <t xml:space="preserve">(10, 5)</t>
   </si>
   <si>
-    <t>(8, 4)</t>
+    <t xml:space="preserve">(8, 4)</t>
   </si>
   <si>
     <t>logistic</t>
@@ -96,21 +98,22 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="2">
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -124,29 +127,35 @@
   </fills>
   <borders count="1">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+  <cellXfs count="3">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -192,13 +201,13 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Angsana New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -226,13 +235,13 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Cordia New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -429,16 +438,235 @@
 </a:theme>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="5" width="18.7109375" customWidth="1"/>
-    <col min="8" max="9" width="20.7109375" customWidth="1"/>
+    <col customWidth="1" min="1" max="5" width="18.7109375"/>
+    <col customWidth="1" min="8" max="9" width="20.7109375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -461,84 +689,84 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>9.07</v>
+        <v>9.0700000000000003</v>
       </c>
       <c r="C2">
-        <v>9.06</v>
+        <v>9.0600000000000005</v>
       </c>
       <c r="D2">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E2">
-        <v>9.999999999999574E-05</v>
+        <v>9.9999999999995736e-05</v>
       </c>
       <c r="H2" t="s">
         <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>8.970000000000001</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="C3">
-        <v>8.960000000000001</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="D3">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E3">
-        <v>9.999999999999574E-05</v>
+        <v>9.9999999999995736e-05</v>
       </c>
       <c r="H3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>8.720000000000001</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="C4">
-        <v>8.73</v>
+        <v>8.7300000000000004</v>
       </c>
       <c r="D4">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E4">
-        <v>9.999999999999574E-05</v>
+        <v>9.9999999999995736e-05</v>
       </c>
       <c r="H4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>9.24</v>
+        <v>9.2400000000000002</v>
       </c>
       <c r="C5">
-        <v>9.24</v>
+        <v>9.2400000000000002</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -547,21 +775,21 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>0.01419990951785619</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>13</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.014199909517856201</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>9.140000000000001</v>
+        <v>9.1400000000000006</v>
       </c>
       <c r="C6">
-        <v>9.140000000000001</v>
+        <v>9.1400000000000006</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -570,36 +798,36 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6">
-        <v>0.009996625536628933</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>14</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.0099966255366289326</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>8.890000000000001</v>
+        <v>8.8900000000000006</v>
       </c>
       <c r="C7">
-        <v>8.91</v>
+        <v>8.9100000000000001</v>
       </c>
       <c r="D7">
         <v>0.01999999999999957</v>
       </c>
       <c r="E7">
-        <v>0.0003999999999999829</v>
+        <v>0.00039999999999998289</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7">
-        <v>0.9998740476378292</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>15</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.99987404763782917</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -613,10 +841,10 @@
         <v>0.01999999999999957</v>
       </c>
       <c r="E8">
-        <v>0.0003999999999999829</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>0.00039999999999998289</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
@@ -627,18 +855,18 @@
         <v>10.23</v>
       </c>
       <c r="D9">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E9">
-        <v>9.999999999999574E-05</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>9.9999999999995736e-05</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>9.99</v>
+        <v>9.9900000000000002</v>
       </c>
       <c r="C10">
         <v>10.01</v>
@@ -647,35 +875,35 @@
         <v>0.01999999999999957</v>
       </c>
       <c r="E10">
-        <v>0.0003999999999999829</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>0.00039999999999998289</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>7.66</v>
+        <v>7.6600000000000001</v>
       </c>
       <c r="C11">
-        <v>7.68</v>
+        <v>7.6799999999999997</v>
       </c>
       <c r="D11">
         <v>0.01999999999999957</v>
       </c>
       <c r="E11">
-        <v>0.0003999999999999829</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>0.00039999999999998289</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>7.57</v>
+        <v>7.5700000000000003</v>
       </c>
       <c r="C12">
-        <v>7.57</v>
+        <v>7.5700000000000003</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -684,41 +912,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>7.32</v>
+        <v>7.3200000000000003</v>
       </c>
       <c r="C13">
-        <v>7.33</v>
+        <v>7.3300000000000001</v>
       </c>
       <c r="D13">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E13">
-        <v>9.999999999999574E-05</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>9.9999999999995736e-05</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>11.53</v>
+        <v>11.529999999999999</v>
       </c>
       <c r="C14">
         <v>11.52</v>
       </c>
       <c r="D14">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E14">
-        <v>9.999999999999574E-05</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>9.9999999999995736e-05</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -729,13 +957,13 @@
         <v>11.42</v>
       </c>
       <c r="D15">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E15">
-        <v>9.999999999999574E-05</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>9.9999999999995736e-05</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16">
         <v>15</v>
       </c>
@@ -752,15 +980,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>8.65</v>
+        <v>8.6500000000000004</v>
       </c>
       <c r="C17">
-        <v>8.65</v>
+        <v>8.6500000000000004</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -769,15 +997,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>8.550000000000001</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="C18">
-        <v>8.550000000000001</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -786,15 +1014,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>8.31</v>
+        <v>8.3100000000000005</v>
       </c>
       <c r="C19">
-        <v>8.31</v>
+        <v>8.3100000000000005</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -803,15 +1031,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>9.890000000000001</v>
+        <v>9.8900000000000006</v>
       </c>
       <c r="C20">
-        <v>9.890000000000001</v>
+        <v>9.8900000000000006</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -820,15 +1048,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>9.789999999999999</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="C21">
-        <v>9.789999999999999</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -837,15 +1065,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>9.550000000000001</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="C22">
-        <v>9.539999999999999</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="D22">
         <v>0.01000000000000156</v>
@@ -854,49 +1082,49 @@
         <v>0.0001000000000000313</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>9.779999999999999</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="C23">
-        <v>9.73</v>
+        <v>9.7300000000000004</v>
       </c>
       <c r="D23">
-        <v>0.04999999999999893</v>
+        <v>0.049999999999998927</v>
       </c>
       <c r="E23">
-        <v>0.002499999999999893</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>0.0024999999999998929</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>9.69</v>
+        <v>9.6899999999999995</v>
       </c>
       <c r="C24">
-        <v>9.67</v>
+        <v>9.6699999999999999</v>
       </c>
       <c r="D24">
         <v>0.01999999999999957</v>
       </c>
       <c r="E24">
-        <v>0.0003999999999999829</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>0.00039999999999998289</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>9.44</v>
+        <v>9.4399999999999995</v>
       </c>
       <c r="C25">
-        <v>9.44</v>
+        <v>9.4399999999999995</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -905,32 +1133,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26">
-        <v>7.19</v>
+        <v>7.1900000000000004</v>
       </c>
       <c r="C26">
-        <v>7.2</v>
+        <v>7.2000000000000002</v>
       </c>
       <c r="D26">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E26">
-        <v>9.999999999999574E-05</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>9.9999999999995736e-05</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27">
-        <v>7.09</v>
+        <v>7.0899999999999999</v>
       </c>
       <c r="C27">
-        <v>7.09</v>
+        <v>7.0899999999999999</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -939,38 +1167,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28">
-        <v>6.84</v>
+        <v>6.8399999999999999</v>
       </c>
       <c r="C28">
-        <v>6.86</v>
+        <v>6.8600000000000003</v>
       </c>
       <c r="D28">
-        <v>0.02000000000000046</v>
+        <v>0.020000000000000458</v>
       </c>
       <c r="E28">
         <v>0.0004000000000000185</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="5" width="18.7109375" customWidth="1"/>
-    <col min="8" max="9" width="20.7109375" customWidth="1"/>
+    <col customWidth="1" min="1" max="5" width="18.7109375"/>
+    <col customWidth="1" min="8" max="9" width="20.7109375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -993,38 +1223,38 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>9.07</v>
+        <v>9.0700000000000003</v>
       </c>
       <c r="C2">
-        <v>9.06</v>
+        <v>9.0600000000000005</v>
       </c>
       <c r="D2">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E2">
-        <v>9.999999999999574E-05</v>
+        <v>9.9999999999995736e-05</v>
       </c>
       <c r="H2" t="s">
         <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>8.970000000000001</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="C3">
-        <v>8.970000000000001</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1033,44 +1263,44 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>8.720000000000001</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="C4">
-        <v>8.699999999999999</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="D4">
         <v>0.02000000000000135</v>
       </c>
       <c r="E4">
-        <v>0.000400000000000054</v>
+        <v>0.00040000000000005401</v>
       </c>
       <c r="H4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>9.24</v>
+        <v>9.2400000000000002</v>
       </c>
       <c r="C5">
-        <v>9.24</v>
+        <v>9.2400000000000002</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1079,44 +1309,44 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I5">
-        <v>0.0173114368051857</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>0.017311436805185699</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>9.140000000000001</v>
+        <v>9.1400000000000006</v>
       </c>
       <c r="C6">
-        <v>9.15</v>
+        <v>9.1500000000000004</v>
       </c>
       <c r="D6">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E6">
-        <v>9.999999999999574E-05</v>
+        <v>9.9999999999995736e-05</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I6">
         <v>0.01296867478511019</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>8.890000000000001</v>
+        <v>8.8900000000000006</v>
       </c>
       <c r="C7">
-        <v>8.890000000000001</v>
+        <v>8.8900000000000006</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1125,13 +1355,13 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I7">
-        <v>0.9998128019190947</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>0.99981280191909472</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1145,10 +1375,10 @@
         <v>0.01999999999999957</v>
       </c>
       <c r="E8">
-        <v>0.0003999999999999829</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>0.00039999999999998289</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1159,55 +1389,55 @@
         <v>10.23</v>
       </c>
       <c r="D9">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E9">
-        <v>9.999999999999574E-05</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>9.9999999999995736e-05</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>9.99</v>
+        <v>9.9900000000000002</v>
       </c>
       <c r="C10">
-        <v>9.98</v>
+        <v>9.9800000000000004</v>
       </c>
       <c r="D10">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E10">
-        <v>9.999999999999574E-05</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>9.9999999999995736e-05</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>7.66</v>
+        <v>7.6600000000000001</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>7.7000000000000002</v>
       </c>
       <c r="D11">
-        <v>0.04000000000000004</v>
+        <v>0.040000000000000042</v>
       </c>
       <c r="E11">
-        <v>0.001600000000000003</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>0.0016000000000000029</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>7.57</v>
+        <v>7.5700000000000003</v>
       </c>
       <c r="C12">
-        <v>7.57</v>
+        <v>7.5700000000000003</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1216,15 +1446,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>7.32</v>
+        <v>7.3200000000000003</v>
       </c>
       <c r="C13">
-        <v>7.32</v>
+        <v>7.3200000000000003</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1233,24 +1463,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>11.53</v>
+        <v>11.529999999999999</v>
       </c>
       <c r="C14">
         <v>11.49</v>
       </c>
       <c r="D14">
-        <v>0.03999999999999915</v>
+        <v>0.039999999999999147</v>
       </c>
       <c r="E14">
         <v>0.001599999999999932</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1267,7 +1497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1278,89 +1508,89 @@
         <v>11.19</v>
       </c>
       <c r="D16">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E16">
-        <v>9.999999999999574E-05</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>9.9999999999995736e-05</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>8.65</v>
+        <v>8.6500000000000004</v>
       </c>
       <c r="C17">
-        <v>8.66</v>
+        <v>8.6600000000000001</v>
       </c>
       <c r="D17">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E17">
-        <v>9.999999999999574E-05</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>9.9999999999995736e-05</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>8.550000000000001</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="C18">
-        <v>8.56</v>
+        <v>8.5600000000000005</v>
       </c>
       <c r="D18">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E18">
-        <v>9.999999999999574E-05</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>9.9999999999995736e-05</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>8.31</v>
+        <v>8.3100000000000005</v>
       </c>
       <c r="C19">
-        <v>8.289999999999999</v>
+        <v>8.2899999999999991</v>
       </c>
       <c r="D19">
         <v>0.02000000000000135</v>
       </c>
       <c r="E19">
-        <v>0.000400000000000054</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>0.00040000000000005401</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>9.890000000000001</v>
+        <v>9.8900000000000006</v>
       </c>
       <c r="C20">
-        <v>9.869999999999999</v>
+        <v>9.8699999999999992</v>
       </c>
       <c r="D20">
         <v>0.02000000000000135</v>
       </c>
       <c r="E20">
-        <v>0.000400000000000054</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>0.00040000000000005401</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>9.789999999999999</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="C21">
-        <v>9.800000000000001</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="D21">
         <v>0.01000000000000156</v>
@@ -1369,100 +1599,100 @@
         <v>0.0001000000000000313</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>9.550000000000001</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="C22">
-        <v>9.51</v>
+        <v>9.5099999999999998</v>
       </c>
       <c r="D22">
-        <v>0.04000000000000092</v>
+        <v>0.040000000000000917</v>
       </c>
       <c r="E22">
         <v>0.001600000000000074</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>9.779999999999999</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="C23">
-        <v>9.789999999999999</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="D23">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E23">
-        <v>9.999999999999574E-05</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>9.9999999999995736e-05</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>9.69</v>
+        <v>9.6899999999999995</v>
       </c>
       <c r="C24">
-        <v>9.68</v>
+        <v>9.6799999999999997</v>
       </c>
       <c r="D24">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E24">
-        <v>9.999999999999574E-05</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>9.9999999999995736e-05</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>9.44</v>
+        <v>9.4399999999999995</v>
       </c>
       <c r="C25">
-        <v>9.470000000000001</v>
+        <v>9.4700000000000006</v>
       </c>
       <c r="D25">
         <v>0.03000000000000114</v>
       </c>
       <c r="E25">
-        <v>0.0009000000000000682</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>0.00090000000000006817</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26">
-        <v>7.19</v>
+        <v>7.1900000000000004</v>
       </c>
       <c r="C26">
-        <v>7.17</v>
+        <v>7.1699999999999999</v>
       </c>
       <c r="D26">
-        <v>0.02000000000000046</v>
+        <v>0.020000000000000458</v>
       </c>
       <c r="E26">
         <v>0.0004000000000000185</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27">
-        <v>7.09</v>
+        <v>7.0899999999999999</v>
       </c>
       <c r="C27">
-        <v>7.09</v>
+        <v>7.0899999999999999</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1471,38 +1701,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28">
-        <v>6.84</v>
+        <v>6.8399999999999999</v>
       </c>
       <c r="C28">
-        <v>6.85</v>
+        <v>6.8499999999999996</v>
       </c>
       <c r="D28">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E28">
-        <v>9.999999999999574E-05</v>
+        <v>9.9999999999995736e-05</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="5" width="18.7109375" customWidth="1"/>
-    <col min="8" max="9" width="20.7109375" customWidth="1"/>
+    <col customWidth="1" min="1" max="5" width="18.7109375"/>
+    <col customWidth="1" min="8" max="9" width="20.7109375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1525,15 +1757,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>9.07</v>
+        <v>9.0700000000000003</v>
       </c>
       <c r="C2">
-        <v>9.07</v>
+        <v>9.0700000000000003</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1548,38 +1780,38 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>8.970000000000001</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="C3">
-        <v>8.949999999999999</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="D3">
         <v>0.02000000000000135</v>
       </c>
       <c r="E3">
-        <v>0.000400000000000054</v>
+        <v>0.00040000000000005401</v>
       </c>
       <c r="H3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>8.720000000000001</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="C4">
-        <v>8.720000000000001</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1588,82 +1820,82 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>9.24</v>
+        <v>9.2400000000000002</v>
       </c>
       <c r="C5">
-        <v>9.23</v>
+        <v>9.2300000000000004</v>
       </c>
       <c r="D5">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E5">
-        <v>9.999999999999574E-05</v>
+        <v>9.9999999999995736e-05</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I5">
-        <v>0.03983563140840875</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>0.039835631408408748</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>9.140000000000001</v>
+        <v>9.1400000000000006</v>
       </c>
       <c r="C6">
-        <v>9.15</v>
+        <v>9.1500000000000004</v>
       </c>
       <c r="D6">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E6">
-        <v>9.999999999999574E-05</v>
+        <v>9.9999999999995736e-05</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I6">
-        <v>0.02965657745370917</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>0.029656577453709171</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>8.890000000000001</v>
+        <v>8.8900000000000006</v>
       </c>
       <c r="C7">
-        <v>8.91</v>
+        <v>8.9100000000000001</v>
       </c>
       <c r="D7">
         <v>0.01999999999999957</v>
       </c>
       <c r="E7">
-        <v>0.0003999999999999829</v>
+        <v>0.00039999999999998289</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I7">
-        <v>0.9990087605608255</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>0.99900876056082555</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1674,13 +1906,13 @@
         <v>10.43</v>
       </c>
       <c r="D8">
-        <v>0.09999999999999964</v>
+        <v>0.099999999999999645</v>
       </c>
       <c r="E8">
-        <v>0.009999999999999929</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>0.0099999999999999291</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1691,98 +1923,98 @@
         <v>10.25</v>
       </c>
       <c r="D9">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E9">
-        <v>9.999999999999574E-05</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>9.9999999999995736e-05</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>9.99</v>
+        <v>9.9900000000000002</v>
       </c>
       <c r="C10">
         <v>10.02</v>
       </c>
       <c r="D10">
-        <v>0.02999999999999936</v>
+        <v>0.029999999999999361</v>
       </c>
       <c r="E10">
-        <v>0.0008999999999999616</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>0.00089999999999996159</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>7.66</v>
+        <v>7.6600000000000001</v>
       </c>
       <c r="C11">
-        <v>7.72</v>
+        <v>7.7199999999999998</v>
       </c>
       <c r="D11">
-        <v>0.05999999999999961</v>
+        <v>0.059999999999999609</v>
       </c>
       <c r="E11">
-        <v>0.003599999999999953</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>0.0035999999999999531</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>7.57</v>
+        <v>7.5700000000000003</v>
       </c>
       <c r="C12">
-        <v>7.53</v>
+        <v>7.5300000000000002</v>
       </c>
       <c r="D12">
-        <v>0.04000000000000004</v>
+        <v>0.040000000000000042</v>
       </c>
       <c r="E12">
-        <v>0.001600000000000003</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>0.0016000000000000029</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>7.32</v>
+        <v>7.3200000000000003</v>
       </c>
       <c r="C13">
-        <v>7.37</v>
+        <v>7.3700000000000001</v>
       </c>
       <c r="D13">
-        <v>0.04999999999999982</v>
+        <v>0.049999999999999822</v>
       </c>
       <c r="E13">
-        <v>0.002499999999999982</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>0.0024999999999999818</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>11.53</v>
+        <v>11.529999999999999</v>
       </c>
       <c r="C14">
         <v>11.49</v>
       </c>
       <c r="D14">
-        <v>0.03999999999999915</v>
+        <v>0.039999999999999147</v>
       </c>
       <c r="E14">
         <v>0.001599999999999932</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1799,7 +2031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1810,21 +2042,21 @@
         <v>11.23</v>
       </c>
       <c r="D16">
-        <v>0.05000000000000071</v>
+        <v>0.050000000000000711</v>
       </c>
       <c r="E16">
-        <v>0.002500000000000071</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>0.0025000000000000712</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>8.65</v>
+        <v>8.6500000000000004</v>
       </c>
       <c r="C17">
-        <v>8.65</v>
+        <v>8.6500000000000004</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1833,15 +2065,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>8.550000000000001</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="C18">
-        <v>8.550000000000001</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1850,49 +2082,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>8.31</v>
+        <v>8.3100000000000005</v>
       </c>
       <c r="C19">
-        <v>8.27</v>
+        <v>8.2699999999999996</v>
       </c>
       <c r="D19">
-        <v>0.04000000000000092</v>
+        <v>0.040000000000000917</v>
       </c>
       <c r="E19">
         <v>0.001600000000000074</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>9.890000000000001</v>
+        <v>9.8900000000000006</v>
       </c>
       <c r="C20">
-        <v>9.949999999999999</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="D20">
-        <v>0.05999999999999872</v>
+        <v>0.059999999999998721</v>
       </c>
       <c r="E20">
-        <v>0.003599999999999846</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>0.0035999999999998459</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>9.789999999999999</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="C21">
-        <v>9.800000000000001</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="D21">
         <v>0.01000000000000156</v>
@@ -1901,49 +2133,49 @@
         <v>0.0001000000000000313</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>9.550000000000001</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="C22">
-        <v>9.52</v>
+        <v>9.5199999999999996</v>
       </c>
       <c r="D22">
         <v>0.03000000000000114</v>
       </c>
       <c r="E22">
-        <v>0.0009000000000000682</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>0.00090000000000006817</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>9.779999999999999</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="C23">
-        <v>9.77</v>
+        <v>9.7699999999999996</v>
       </c>
       <c r="D23">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E23">
-        <v>9.999999999999574E-05</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>9.9999999999995736e-05</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>9.69</v>
+        <v>9.6899999999999995</v>
       </c>
       <c r="C24">
-        <v>9.69</v>
+        <v>9.6899999999999995</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1952,89 +2184,91 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>9.44</v>
+        <v>9.4399999999999995</v>
       </c>
       <c r="C25">
-        <v>9.460000000000001</v>
+        <v>9.4600000000000009</v>
       </c>
       <c r="D25">
         <v>0.02000000000000135</v>
       </c>
       <c r="E25">
-        <v>0.000400000000000054</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>0.00040000000000005401</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26">
-        <v>7.19</v>
+        <v>7.1900000000000004</v>
       </c>
       <c r="C26">
-        <v>7.27</v>
+        <v>7.2699999999999996</v>
       </c>
       <c r="D26">
-        <v>0.07999999999999918</v>
+        <v>0.079999999999999183</v>
       </c>
       <c r="E26">
-        <v>0.006399999999999869</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>0.0063999999999998693</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27">
-        <v>7.09</v>
+        <v>7.0899999999999999</v>
       </c>
       <c r="C27">
-        <v>7.07</v>
+        <v>7.0700000000000003</v>
       </c>
       <c r="D27">
         <v>0.01999999999999957</v>
       </c>
       <c r="E27">
-        <v>0.0003999999999999829</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>0.00039999999999998289</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28">
-        <v>6.84</v>
+        <v>6.8399999999999999</v>
       </c>
       <c r="C28">
-        <v>6.92</v>
+        <v>6.9199999999999999</v>
       </c>
       <c r="D28">
-        <v>0.08000000000000007</v>
+        <v>0.080000000000000071</v>
       </c>
       <c r="E28">
-        <v>0.006400000000000012</v>
+        <v>0.0064000000000000116</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="5" width="18.7109375" customWidth="1"/>
-    <col min="8" max="9" width="20.7109375" customWidth="1"/>
+    <col customWidth="1" min="1" max="5" width="18.7109375"/>
+    <col customWidth="1" min="8" max="9" width="20.7109375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2057,21 +2291,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>9.07</v>
+        <v>9.0700000000000003</v>
       </c>
       <c r="C2">
-        <v>8.98</v>
+        <v>8.9800000000000004</v>
       </c>
       <c r="D2">
-        <v>0.08999999999999986</v>
+        <v>0.089999999999999858</v>
       </c>
       <c r="E2">
-        <v>0.008099999999999975</v>
+        <v>0.0080999999999999753</v>
       </c>
       <c r="H2" t="s">
         <v>7</v>
@@ -2080,122 +2314,122 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>8.970000000000001</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="C3">
-        <v>8.99</v>
+        <v>8.9900000000000002</v>
       </c>
       <c r="D3">
         <v>0.01999999999999957</v>
       </c>
       <c r="E3">
-        <v>0.0003999999999999829</v>
+        <v>0.00039999999999998289</v>
       </c>
       <c r="H3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>8.720000000000001</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="C4">
-        <v>8.699999999999999</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="D4">
         <v>0.02000000000000135</v>
       </c>
       <c r="E4">
-        <v>0.000400000000000054</v>
+        <v>0.00040000000000005401</v>
       </c>
       <c r="H4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>9.24</v>
+        <v>9.2400000000000002</v>
       </c>
       <c r="C5">
-        <v>9.19</v>
+        <v>9.1899999999999995</v>
       </c>
       <c r="D5">
-        <v>0.05000000000000071</v>
+        <v>0.050000000000000711</v>
       </c>
       <c r="E5">
-        <v>0.002500000000000071</v>
+        <v>0.0025000000000000712</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I5">
-        <v>0.04573058975366982</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>0.045730589753669823</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>9.140000000000001</v>
+        <v>9.1400000000000006</v>
       </c>
       <c r="C6">
-        <v>9.119999999999999</v>
+        <v>9.1199999999999992</v>
       </c>
       <c r="D6">
         <v>0.02000000000000135</v>
       </c>
       <c r="E6">
-        <v>0.000400000000000054</v>
+        <v>0.00040000000000005401</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I6">
-        <v>0.03486586386576107</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>0.034865863865761071</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>8.890000000000001</v>
+        <v>8.8900000000000006</v>
       </c>
       <c r="C7">
-        <v>8.84</v>
+        <v>8.8399999999999999</v>
       </c>
       <c r="D7">
-        <v>0.05000000000000071</v>
+        <v>0.050000000000000711</v>
       </c>
       <c r="E7">
-        <v>0.002500000000000071</v>
+        <v>0.0025000000000000712</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I7">
-        <v>0.9986936824330463</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>0.99869368243304635</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2212,7 +2446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2226,95 +2460,95 @@
         <v>0.01999999999999957</v>
       </c>
       <c r="E9">
-        <v>0.0003999999999999829</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>0.00039999999999998289</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>9.99</v>
+        <v>9.9900000000000002</v>
       </c>
       <c r="C10">
-        <v>9.9</v>
+        <v>9.9000000000000004</v>
       </c>
       <c r="D10">
-        <v>0.08999999999999986</v>
+        <v>0.089999999999999858</v>
       </c>
       <c r="E10">
-        <v>0.008099999999999975</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>0.0080999999999999753</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>7.66</v>
+        <v>7.6600000000000001</v>
       </c>
       <c r="C11">
         <v>7.71</v>
       </c>
       <c r="D11">
-        <v>0.04999999999999982</v>
+        <v>0.049999999999999822</v>
       </c>
       <c r="E11">
-        <v>0.002499999999999982</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>0.0024999999999999818</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>7.57</v>
+        <v>7.5700000000000003</v>
       </c>
       <c r="C12">
-        <v>7.55</v>
+        <v>7.5499999999999998</v>
       </c>
       <c r="D12">
-        <v>0.02000000000000046</v>
+        <v>0.020000000000000458</v>
       </c>
       <c r="E12">
         <v>0.0004000000000000185</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>7.32</v>
+        <v>7.3200000000000003</v>
       </c>
       <c r="C13">
-        <v>7.44</v>
+        <v>7.4400000000000004</v>
       </c>
       <c r="D13">
-        <v>0.1200000000000001</v>
+        <v>0.12000000000000011</v>
       </c>
       <c r="E13">
-        <v>0.01440000000000003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>0.014400000000000031</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>11.53</v>
+        <v>11.529999999999999</v>
       </c>
       <c r="C14">
         <v>11.5</v>
       </c>
       <c r="D14">
-        <v>0.02999999999999936</v>
+        <v>0.029999999999999361</v>
       </c>
       <c r="E14">
-        <v>0.0008999999999999616</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>0.00089999999999996159</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2331,7 +2565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2342,38 +2576,38 @@
         <v>11.23</v>
       </c>
       <c r="D16">
-        <v>0.05000000000000071</v>
+        <v>0.050000000000000711</v>
       </c>
       <c r="E16">
-        <v>0.002500000000000071</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>0.0025000000000000712</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>8.65</v>
+        <v>8.6500000000000004</v>
       </c>
       <c r="C17">
-        <v>8.630000000000001</v>
+        <v>8.6300000000000008</v>
       </c>
       <c r="D17">
         <v>0.01999999999999957</v>
       </c>
       <c r="E17">
-        <v>0.0003999999999999829</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>0.00039999999999998289</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>8.550000000000001</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="C18">
-        <v>8.539999999999999</v>
+        <v>8.5399999999999991</v>
       </c>
       <c r="D18">
         <v>0.01000000000000156</v>
@@ -2382,100 +2616,100 @@
         <v>0.0001000000000000313</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>8.31</v>
+        <v>8.3100000000000005</v>
       </c>
       <c r="C19">
-        <v>8.34</v>
+        <v>8.3399999999999999</v>
       </c>
       <c r="D19">
-        <v>0.02999999999999936</v>
+        <v>0.029999999999999361</v>
       </c>
       <c r="E19">
-        <v>0.0008999999999999616</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>0.00089999999999996159</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>9.890000000000001</v>
+        <v>9.8900000000000006</v>
       </c>
       <c r="C20">
-        <v>9.869999999999999</v>
+        <v>9.8699999999999992</v>
       </c>
       <c r="D20">
         <v>0.02000000000000135</v>
       </c>
       <c r="E20">
-        <v>0.000400000000000054</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>0.00040000000000005401</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>9.789999999999999</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="C21">
-        <v>9.83</v>
+        <v>9.8300000000000001</v>
       </c>
       <c r="D21">
-        <v>0.04000000000000092</v>
+        <v>0.040000000000000917</v>
       </c>
       <c r="E21">
         <v>0.001600000000000074</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>9.550000000000001</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="C22">
-        <v>9.470000000000001</v>
+        <v>9.4700000000000006</v>
       </c>
       <c r="D22">
-        <v>0.08000000000000007</v>
+        <v>0.080000000000000071</v>
       </c>
       <c r="E22">
-        <v>0.006400000000000012</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>0.0064000000000000116</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>9.779999999999999</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="C23">
-        <v>9.74</v>
+        <v>9.7400000000000002</v>
       </c>
       <c r="D23">
-        <v>0.03999999999999915</v>
+        <v>0.039999999999999147</v>
       </c>
       <c r="E23">
         <v>0.001599999999999932</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>9.69</v>
+        <v>9.6899999999999995</v>
       </c>
       <c r="C24">
-        <v>9.69</v>
+        <v>9.6899999999999995</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -2484,89 +2718,91 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>9.44</v>
+        <v>9.4399999999999995</v>
       </c>
       <c r="C25">
-        <v>9.460000000000001</v>
+        <v>9.4600000000000009</v>
       </c>
       <c r="D25">
         <v>0.02000000000000135</v>
       </c>
       <c r="E25">
-        <v>0.000400000000000054</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>0.00040000000000005401</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26">
-        <v>7.19</v>
+        <v>7.1900000000000004</v>
       </c>
       <c r="C26">
-        <v>7.23</v>
+        <v>7.2300000000000004</v>
       </c>
       <c r="D26">
-        <v>0.04000000000000004</v>
+        <v>0.040000000000000042</v>
       </c>
       <c r="E26">
-        <v>0.001600000000000003</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>0.0016000000000000029</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27">
-        <v>7.09</v>
+        <v>7.0899999999999999</v>
       </c>
       <c r="C27">
-        <v>7.08</v>
+        <v>7.0800000000000001</v>
       </c>
       <c r="D27">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E27">
-        <v>9.999999999999574E-05</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>9.9999999999995736e-05</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28">
-        <v>6.84</v>
+        <v>6.8399999999999999</v>
       </c>
       <c r="C28">
-        <v>6.85</v>
+        <v>6.8499999999999996</v>
       </c>
       <c r="D28">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E28">
-        <v>9.999999999999574E-05</v>
+        <v>9.9999999999995736e-05</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="5" width="18.7109375" customWidth="1"/>
-    <col min="8" max="9" width="20.7109375" customWidth="1"/>
+    <col customWidth="1" min="1" max="5" width="18.7109375"/>
+    <col customWidth="1" min="8" max="9" width="20.7109375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2589,21 +2825,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>9.07</v>
+        <v>9.0700000000000003</v>
       </c>
       <c r="C2">
-        <v>9.09</v>
+        <v>9.0899999999999999</v>
       </c>
       <c r="D2">
         <v>0.01999999999999957</v>
       </c>
       <c r="E2">
-        <v>0.0003999999999999829</v>
+        <v>0.00039999999999998289</v>
       </c>
       <c r="H2" t="s">
         <v>7</v>
@@ -2612,122 +2848,122 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>8.970000000000001</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="C3">
-        <v>8.949999999999999</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="D3">
         <v>0.02000000000000135</v>
       </c>
       <c r="E3">
-        <v>0.000400000000000054</v>
+        <v>0.00040000000000005401</v>
       </c>
       <c r="H3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>8.720000000000001</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="C4">
-        <v>8.73</v>
+        <v>8.7300000000000004</v>
       </c>
       <c r="D4">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E4">
-        <v>9.999999999999574E-05</v>
+        <v>9.9999999999995736e-05</v>
       </c>
       <c r="H4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>9.24</v>
+        <v>9.2400000000000002</v>
       </c>
       <c r="C5">
-        <v>9.27</v>
+        <v>9.2699999999999996</v>
       </c>
       <c r="D5">
-        <v>0.02999999999999936</v>
+        <v>0.029999999999999361</v>
       </c>
       <c r="E5">
-        <v>0.0008999999999999616</v>
+        <v>0.00089999999999996159</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I5">
-        <v>0.04580694418219362</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>0.045806944182193617</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>9.140000000000001</v>
+        <v>9.1400000000000006</v>
       </c>
       <c r="C6">
-        <v>9.119999999999999</v>
+        <v>9.1199999999999992</v>
       </c>
       <c r="D6">
         <v>0.02000000000000135</v>
       </c>
       <c r="E6">
-        <v>0.000400000000000054</v>
+        <v>0.00040000000000005401</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I6">
-        <v>0.03351571075210094</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>0.033515710752100941</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>8.890000000000001</v>
+        <v>8.8900000000000006</v>
       </c>
       <c r="C7">
-        <v>8.9</v>
+        <v>8.9000000000000004</v>
       </c>
       <c r="D7">
-        <v>0.009999999999999787</v>
+        <v>0.0099999999999997868</v>
       </c>
       <c r="E7">
-        <v>9.999999999999574E-05</v>
+        <v>9.9999999999995736e-05</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I7">
-        <v>0.9986893165851414</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>0.99868931658514137</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2738,13 +2974,13 @@
         <v>10.42</v>
       </c>
       <c r="D8">
-        <v>0.08999999999999986</v>
+        <v>0.089999999999999858</v>
       </c>
       <c r="E8">
-        <v>0.008099999999999975</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>0.0080999999999999753</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2752,21 +2988,21 @@
         <v>10.24</v>
       </c>
       <c r="C9">
-        <v>10.22</v>
+        <v>10.220000000000001</v>
       </c>
       <c r="D9">
         <v>0.01999999999999957</v>
       </c>
       <c r="E9">
-        <v>0.0003999999999999829</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>0.00039999999999998289</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>9.99</v>
+        <v>9.9900000000000002</v>
       </c>
       <c r="C10">
         <v>10.01</v>
@@ -2775,35 +3011,35 @@
         <v>0.01999999999999957</v>
       </c>
       <c r="E10">
-        <v>0.0003999999999999829</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>0.00039999999999998289</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>7.66</v>
+        <v>7.6600000000000001</v>
       </c>
       <c r="C11">
         <v>7.71</v>
       </c>
       <c r="D11">
-        <v>0.04999999999999982</v>
+        <v>0.049999999999999822</v>
       </c>
       <c r="E11">
-        <v>0.002499999999999982</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>0.0024999999999999818</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>7.57</v>
+        <v>7.5700000000000003</v>
       </c>
       <c r="C12">
-        <v>7.57</v>
+        <v>7.5700000000000003</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -2812,41 +3048,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>7.32</v>
+        <v>7.3200000000000003</v>
       </c>
       <c r="C13">
-        <v>7.45</v>
+        <v>7.4500000000000002</v>
       </c>
       <c r="D13">
-        <v>0.1299999999999999</v>
+        <v>0.12999999999999989</v>
       </c>
       <c r="E13">
-        <v>0.01689999999999997</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>0.016899999999999971</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>11.53</v>
+        <v>11.529999999999999</v>
       </c>
       <c r="C14">
         <v>11.48</v>
       </c>
       <c r="D14">
-        <v>0.04999999999999893</v>
+        <v>0.049999999999998927</v>
       </c>
       <c r="E14">
-        <v>0.002499999999999893</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>0.0024999999999998929</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2854,16 +3090,16 @@
         <v>11.43</v>
       </c>
       <c r="C15">
-        <v>11.37</v>
+        <v>11.369999999999999</v>
       </c>
       <c r="D15">
-        <v>0.0600000000000005</v>
+        <v>0.060000000000000497</v>
       </c>
       <c r="E15">
-        <v>0.00360000000000006</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>0.0036000000000000602</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2880,49 +3116,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>8.65</v>
+        <v>8.6500000000000004</v>
       </c>
       <c r="C17">
-        <v>8.68</v>
+        <v>8.6799999999999997</v>
       </c>
       <c r="D17">
-        <v>0.02999999999999936</v>
+        <v>0.029999999999999361</v>
       </c>
       <c r="E17">
-        <v>0.0008999999999999616</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>0.00089999999999996159</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>8.550000000000001</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="C18">
-        <v>8.529999999999999</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="D18">
         <v>0.02000000000000135</v>
       </c>
       <c r="E18">
-        <v>0.000400000000000054</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>0.00040000000000005401</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>8.31</v>
+        <v>8.3100000000000005</v>
       </c>
       <c r="C19">
-        <v>8.31</v>
+        <v>8.3100000000000005</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -2931,66 +3167,66 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>9.890000000000001</v>
+        <v>9.8900000000000006</v>
       </c>
       <c r="C20">
-        <v>9.949999999999999</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="D20">
-        <v>0.05999999999999872</v>
+        <v>0.059999999999998721</v>
       </c>
       <c r="E20">
-        <v>0.003599999999999846</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>0.0035999999999998459</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>9.789999999999999</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="C21">
-        <v>9.73</v>
+        <v>9.7300000000000004</v>
       </c>
       <c r="D21">
-        <v>0.05999999999999872</v>
+        <v>0.059999999999998721</v>
       </c>
       <c r="E21">
-        <v>0.003599999999999846</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>0.0035999999999998459</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>9.550000000000001</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="C22">
-        <v>9.52</v>
+        <v>9.5199999999999996</v>
       </c>
       <c r="D22">
         <v>0.03000000000000114</v>
       </c>
       <c r="E22">
-        <v>0.0009000000000000682</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>0.00090000000000006817</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>9.779999999999999</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="C23">
-        <v>9.779999999999999</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -2999,32 +3235,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>9.69</v>
+        <v>9.6899999999999995</v>
       </c>
       <c r="C24">
-        <v>9.65</v>
+        <v>9.6500000000000004</v>
       </c>
       <c r="D24">
-        <v>0.03999999999999915</v>
+        <v>0.039999999999999147</v>
       </c>
       <c r="E24">
         <v>0.001599999999999932</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>9.44</v>
+        <v>9.4399999999999995</v>
       </c>
       <c r="C25">
-        <v>9.44</v>
+        <v>9.4399999999999995</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -3033,12 +3269,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26">
-        <v>7.19</v>
+        <v>7.1900000000000004</v>
       </c>
       <c r="C26">
         <v>7.21</v>
@@ -3047,65 +3283,67 @@
         <v>0.01999999999999957</v>
       </c>
       <c r="E26">
-        <v>0.0003999999999999829</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>0.00039999999999998289</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27">
-        <v>7.09</v>
+        <v>7.0899999999999999</v>
       </c>
       <c r="C27">
-        <v>7.07</v>
+        <v>7.0700000000000003</v>
       </c>
       <c r="D27">
         <v>0.01999999999999957</v>
       </c>
       <c r="E27">
-        <v>0.0003999999999999829</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>0.00039999999999998289</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28">
-        <v>6.84</v>
+        <v>6.8399999999999999</v>
       </c>
       <c r="C28">
-        <v>6.92</v>
+        <v>6.9199999999999999</v>
       </c>
       <c r="D28">
-        <v>0.08000000000000007</v>
+        <v>0.080000000000000071</v>
       </c>
       <c r="E28">
-        <v>0.006400000000000012</v>
+        <v>0.0064000000000000116</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="6" width="15.7109375" customWidth="1"/>
+    <col customWidth="1" min="1" max="6" width="15.7109375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1">
       <c r="A1" t="s">
         <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D1" t="s">
         <v>20</v>
@@ -3117,87 +3355,87 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>0.01</v>
       </c>
       <c r="D2">
-        <v>0.9998740476378292</v>
+        <v>0.99987404763782917</v>
       </c>
       <c r="E2">
         <v>0.01419990951785619</v>
       </c>
       <c r="F2">
-        <v>0.009996625536628933</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>0.0099966255366289326</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>0.001</v>
       </c>
       <c r="D3">
-        <v>0.9998128019190947</v>
+        <v>0.99981280191909472</v>
       </c>
       <c r="E3">
-        <v>0.0173114368051857</v>
+        <v>0.017311436805185699</v>
       </c>
       <c r="F3">
         <v>0.01296867478511019</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4">
       <c r="A4" t="s">
         <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <v>0.01</v>
       </c>
       <c r="D4">
-        <v>0.9990087605608255</v>
+        <v>0.99900876056082555</v>
       </c>
       <c r="E4">
-        <v>0.03983563140840875</v>
+        <v>0.039835631408408748</v>
       </c>
       <c r="F4">
-        <v>0.02965657745370917</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>0.029656577453709171</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>0.001</v>
       </c>
       <c r="D5">
-        <v>0.9986936824330463</v>
+        <v>0.99869368243304635</v>
       </c>
       <c r="E5">
-        <v>0.04573058975366982</v>
+        <v>0.045730589753669823</v>
       </c>
       <c r="F5">
-        <v>0.03486586386576107</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>0.034865863865761071</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -3208,16 +3446,16 @@
         <v>0.01</v>
       </c>
       <c r="D6">
-        <v>0.9986893165851414</v>
+        <v>0.99868931658514137</v>
       </c>
       <c r="E6">
-        <v>0.04580694418219362</v>
+        <v>0.045806944182193617</v>
       </c>
       <c r="F6">
-        <v>0.03351571075210094</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>0.033515710752100941</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -3228,16 +3466,16 @@
         <v>0.001</v>
       </c>
       <c r="D7">
-        <v>0.9986694871947592</v>
+        <v>0.99866948719475923</v>
       </c>
       <c r="E7">
-        <v>0.04615215111578969</v>
+        <v>0.046152151115789693</v>
       </c>
       <c r="F7">
         <v>0.02683747510206394</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -3248,56 +3486,56 @@
         <v>0.01</v>
       </c>
       <c r="D8">
-        <v>0.9986266346393943</v>
+        <v>0.99862663463939427</v>
       </c>
       <c r="E8">
-        <v>0.04688948505186386</v>
+        <v>0.046889485051863862</v>
       </c>
       <c r="F8">
         <v>0.03465595224986337</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C9">
         <v>0.001</v>
       </c>
       <c r="D9">
-        <v>0.9982939762279739</v>
+        <v>0.99829397622797389</v>
       </c>
       <c r="E9">
-        <v>0.05226066814554303</v>
+        <v>0.052260668145543032</v>
       </c>
       <c r="F9">
-        <v>0.03974509423974745</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>0.039745094239747453</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C10">
         <v>0.01</v>
       </c>
       <c r="D10">
-        <v>0.9982667577244222</v>
+        <v>0.99826675772442219</v>
       </c>
       <c r="E10">
-        <v>0.05267591101088784</v>
+        <v>0.052675911010887838</v>
       </c>
       <c r="F10">
-        <v>0.03724328292522854</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>0.037243282925228542</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -3305,19 +3543,19 @@
         <v>23</v>
       </c>
       <c r="C11">
-        <v>0.1</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="D11">
-        <v>0.9977440921890663</v>
+        <v>0.99774409218906635</v>
       </c>
       <c r="E11">
-        <v>0.06009565770680979</v>
+        <v>0.060095657706809788</v>
       </c>
       <c r="F11">
-        <v>0.045077793114763</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>0.045077793114763003</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -3328,16 +3566,16 @@
         <v>0.001</v>
       </c>
       <c r="D12">
-        <v>0.9974315494691606</v>
+        <v>0.99743154946916057</v>
       </c>
       <c r="E12">
-        <v>0.06412361845957301</v>
+        <v>0.064123618459573012</v>
       </c>
       <c r="F12">
-        <v>0.04326917377119745</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>0.043269173771197447</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -3351,13 +3589,13 @@
         <v>0.9971343489086919</v>
       </c>
       <c r="E13">
-        <v>0.06773202724460121</v>
+        <v>0.067732027244601214</v>
       </c>
       <c r="F13">
-        <v>0.03948955952846661</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>0.039489559528466611</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -3368,38 +3606,38 @@
         <v>0.01</v>
       </c>
       <c r="D14">
-        <v>0.996098610711061</v>
+        <v>0.99609861071106098</v>
       </c>
       <c r="E14">
-        <v>0.07903001461819756</v>
+        <v>0.079030014618197558</v>
       </c>
       <c r="F14">
-        <v>0.0600876988909808</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>0.060087698890980798</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C15">
-        <v>0.1</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="D15">
-        <v>0.9958820597149857</v>
+        <v>0.99588205971498567</v>
       </c>
       <c r="E15">
-        <v>0.08119372023228184</v>
+        <v>0.081193720232281844</v>
       </c>
       <c r="F15">
-        <v>0.05751245737252301</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>0.057512457372523008</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
@@ -3408,36 +3646,36 @@
         <v>0.01</v>
       </c>
       <c r="D16">
-        <v>0.9953467303675642</v>
+        <v>0.99534673036756416</v>
       </c>
       <c r="E16">
-        <v>0.086310081715942</v>
+        <v>0.086310081715941997</v>
       </c>
       <c r="F16">
-        <v>0.06776464458594118</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>0.067764644585941183</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C17">
-        <v>0.1</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="D17">
-        <v>0.9950340204539226</v>
+        <v>0.99503402045392264</v>
       </c>
       <c r="E17">
-        <v>0.08916304299309656</v>
+        <v>0.089163042993096561</v>
       </c>
       <c r="F17">
-        <v>0.07684238850022765</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>0.076842388500227649</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -3445,19 +3683,19 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>0.1</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="D18">
-        <v>0.9948012027248543</v>
+        <v>0.99480120272485428</v>
       </c>
       <c r="E18">
-        <v>0.0912291986218028</v>
+        <v>0.091229198621802801</v>
       </c>
       <c r="F18">
-        <v>0.07708712420548249</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>0.077087124205482485</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -3465,39 +3703,39 @@
         <v>23</v>
       </c>
       <c r="C19">
-        <v>0.3</v>
+        <v>0.29999999999999999</v>
       </c>
       <c r="D19">
-        <v>0.994694777667553</v>
+        <v>0.99469477766755299</v>
       </c>
       <c r="E19">
-        <v>0.09215824870074921</v>
+        <v>0.092158248700749207</v>
       </c>
       <c r="F19">
-        <v>0.07331293860755875</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>0.073312938607558747</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" t="s">
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C20">
-        <v>0.1</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="D20">
         <v>0.9943090340877565</v>
       </c>
       <c r="E20">
-        <v>0.09544988528031058</v>
+        <v>0.095449885280310579</v>
       </c>
       <c r="F20">
-        <v>0.06851081432771497</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>0.068510814327714969</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -3508,18 +3746,18 @@
         <v>0.001</v>
       </c>
       <c r="D21">
-        <v>0.9942138770399999</v>
+        <v>0.99421387703999986</v>
       </c>
       <c r="E21">
-        <v>0.09624457252063967</v>
+        <v>0.096244572520639671</v>
       </c>
       <c r="F21">
-        <v>0.076850335224556</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>0.076850335224556005</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
         <v>19</v>
@@ -3528,16 +3766,16 @@
         <v>0.001</v>
       </c>
       <c r="D22">
-        <v>0.9928363964240429</v>
+        <v>0.99283639642404287</v>
       </c>
       <c r="E22">
         <v>0.1070898205713226</v>
       </c>
       <c r="F22">
-        <v>0.07502115340330878</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>0.075021153403308782</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -3548,16 +3786,16 @@
         <v>0.001</v>
       </c>
       <c r="D23">
-        <v>0.9919470185243341</v>
+        <v>0.99194701852433409</v>
       </c>
       <c r="E23">
-        <v>0.1135431055750944</v>
+        <v>0.11354310557509439</v>
       </c>
       <c r="F23">
-        <v>0.07547442964028603</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>0.075474429640286028</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -3565,39 +3803,39 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>0.3</v>
+        <v>0.29999999999999999</v>
       </c>
       <c r="D24">
-        <v>0.9887885980466377</v>
+        <v>0.98878859804663766</v>
       </c>
       <c r="E24">
-        <v>0.133971487756524</v>
+        <v>0.13397148775652401</v>
       </c>
       <c r="F24">
-        <v>0.104509419150829</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>0.10450941915082899</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" t="s">
         <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C25">
-        <v>0.3</v>
+        <v>0.29999999999999999</v>
       </c>
       <c r="D25">
-        <v>0.9879913215007015</v>
+        <v>0.98799132150070146</v>
       </c>
       <c r="E25">
         <v>0.1386532416256612</v>
       </c>
       <c r="F25">
-        <v>0.1056595567334491</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>0.10565955673344909</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -3608,56 +3846,56 @@
         <v>0.5</v>
       </c>
       <c r="D26">
-        <v>0.9878095500822582</v>
+        <v>0.98780955008225824</v>
       </c>
       <c r="E26">
-        <v>0.1396986746571842</v>
+        <v>0.13969867465718419</v>
       </c>
       <c r="F26">
-        <v>0.1087300816858155</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>0.10873008168581549</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>0.3</v>
+        <v>0.29999999999999999</v>
       </c>
       <c r="D27">
-        <v>0.9834959868472068</v>
+        <v>0.98349598684720685</v>
       </c>
       <c r="E27">
-        <v>0.1625463415245985</v>
+        <v>0.16254634152459849</v>
       </c>
       <c r="F27">
-        <v>0.1297163311323941</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>0.12971633113239411</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" t="s">
         <v>18</v>
       </c>
       <c r="B28" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C28">
-        <v>0.3</v>
+        <v>0.29999999999999999</v>
       </c>
       <c r="D28">
-        <v>0.9801834103792629</v>
+        <v>0.98018341037926293</v>
       </c>
       <c r="E28">
-        <v>0.1781135158694137</v>
+        <v>0.17811351586941371</v>
       </c>
       <c r="F28">
-        <v>0.130311294188633</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <v>0.13031129418863299</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" t="s">
         <v>17</v>
       </c>
@@ -3665,19 +3903,19 @@
         <v>19</v>
       </c>
       <c r="C29">
-        <v>0.1</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="D29">
-        <v>0.9790554172974714</v>
+        <v>0.97905541729747136</v>
       </c>
       <c r="E29">
         <v>0.1831126191458155</v>
       </c>
       <c r="F29">
-        <v>0.1376730128014582</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>0.13767301280145819</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -3685,30 +3923,30 @@
         <v>19</v>
       </c>
       <c r="C30">
-        <v>0.1</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="D30">
-        <v>0.9775833188620209</v>
+        <v>0.97758331886202088</v>
       </c>
       <c r="E30">
         <v>0.1894384256391248</v>
       </c>
       <c r="F30">
-        <v>0.1507012910561114</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>0.15070129105611141</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B31" t="s">
         <v>19</v>
       </c>
       <c r="C31">
-        <v>0.1</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="D31">
-        <v>0.9749403768518595</v>
+        <v>0.97494037685185952</v>
       </c>
       <c r="E31">
         <v>0.2002948055640405</v>
@@ -3717,7 +3955,7 @@
         <v>0.1550439123990679</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -3728,76 +3966,76 @@
         <v>0.5</v>
       </c>
       <c r="D32">
-        <v>0.9748665029982038</v>
+        <v>0.97486650299820377</v>
       </c>
       <c r="E32">
-        <v>0.2005898151963983</v>
+        <v>0.20058981519639829</v>
       </c>
       <c r="F32">
         <v>0.156702908099592</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C33">
         <v>0.5</v>
       </c>
       <c r="D33">
-        <v>0.9607295335145913</v>
+        <v>0.96072953351459134</v>
       </c>
       <c r="E33">
-        <v>0.2507352814697409</v>
+        <v>0.25073528146974089</v>
       </c>
       <c r="F33">
-        <v>0.1920154069290896</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>0.19201540692908961</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" t="s">
         <v>18</v>
       </c>
       <c r="B34" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C34">
         <v>0.5</v>
       </c>
       <c r="D34">
-        <v>0.929691774442351</v>
+        <v>0.92969177444235096</v>
       </c>
       <c r="E34">
-        <v>0.3354945636688049</v>
+        <v>0.33549456366880492</v>
       </c>
       <c r="F34">
-        <v>0.2243102955332195</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+        <v>0.22431029553321949</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" t="s">
         <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C35">
         <v>0.5</v>
       </c>
       <c r="D35">
-        <v>0.9077078141374264</v>
+        <v>0.90770781413742641</v>
       </c>
       <c r="E35">
-        <v>0.3843836307248614</v>
+        <v>0.38438363072486142</v>
       </c>
       <c r="F35">
-        <v>0.2455852205584235</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>0.24558522055842349</v>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -3805,19 +4043,19 @@
         <v>19</v>
       </c>
       <c r="C36">
-        <v>0.3</v>
+        <v>0.29999999999999999</v>
       </c>
       <c r="D36">
-        <v>0.847859281566518</v>
+        <v>0.84785928156651802</v>
       </c>
       <c r="E36">
-        <v>0.4935204463104573</v>
+        <v>0.49352044631045727</v>
       </c>
       <c r="F36">
-        <v>0.3699808514752871</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <v>0.36998085147528709</v>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -3825,41 +4063,41 @@
         <v>19</v>
       </c>
       <c r="C37">
-        <v>0.3</v>
+        <v>0.29999999999999999</v>
       </c>
       <c r="D37">
-        <v>0.8402473345729748</v>
+        <v>0.84024733457297485</v>
       </c>
       <c r="E37">
-        <v>0.5057157448796749</v>
+        <v>0.50571574487967486</v>
       </c>
       <c r="F37">
-        <v>0.3793705001293695</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <v>0.37937050012936951</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B38" t="s">
         <v>19</v>
       </c>
       <c r="C38">
-        <v>0.3</v>
+        <v>0.29999999999999999</v>
       </c>
       <c r="D38">
-        <v>0.802674171616055</v>
+        <v>0.80267417161605503</v>
       </c>
       <c r="E38">
-        <v>0.562049267249865</v>
+        <v>0.56204926724986504</v>
       </c>
       <c r="F38">
-        <v>0.4543577830005471</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>0.45435778300054708</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B39" t="s">
         <v>23</v>
@@ -3868,58 +4106,58 @@
         <v>0.5</v>
       </c>
       <c r="D39">
-        <v>0.7470976812406513</v>
+        <v>0.74709768124065135</v>
       </c>
       <c r="E39">
-        <v>0.6362954595628785</v>
+        <v>0.63629545956287847</v>
       </c>
       <c r="F39">
         <v>0.4894113321503536</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B40" t="s">
         <v>23</v>
       </c>
       <c r="C40">
-        <v>0.3</v>
+        <v>0.29999999999999999</v>
       </c>
       <c r="D40">
         <v>0.7469664210330218</v>
       </c>
       <c r="E40">
-        <v>0.6364605617261941</v>
+        <v>0.63646056172619414</v>
       </c>
       <c r="F40">
-        <v>0.4825665233284936</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+        <v>0.48256652332849359</v>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B41" t="s">
         <v>23</v>
       </c>
       <c r="C41">
-        <v>0.1</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="D41">
-        <v>0.7410733177826321</v>
+        <v>0.74107331778263208</v>
       </c>
       <c r="E41">
-        <v>0.6438294256779989</v>
+        <v>0.64382942567799895</v>
       </c>
       <c r="F41">
-        <v>0.4650947469851175</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>0.46509474698511749</v>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B42" t="s">
         <v>23</v>
@@ -3928,18 +4166,18 @@
         <v>0.01</v>
       </c>
       <c r="D42">
-        <v>0.7353119927975595</v>
+        <v>0.73531199279755954</v>
       </c>
       <c r="E42">
-        <v>0.6509528769217118</v>
+        <v>0.65095287692171178</v>
       </c>
       <c r="F42">
-        <v>0.4680216244949879</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+        <v>0.46802162449498791</v>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B43" t="s">
         <v>23</v>
@@ -3948,18 +4186,18 @@
         <v>0.001</v>
       </c>
       <c r="D43">
-        <v>0.7348525599453735</v>
+        <v>0.73485255994537346</v>
       </c>
       <c r="E43">
-        <v>0.6515175785019908</v>
+        <v>0.65151757850199077</v>
       </c>
       <c r="F43">
-        <v>0.4649293579857346</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+        <v>0.46492935798573459</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B44" t="s">
         <v>19</v>
@@ -3968,16 +4206,16 @@
         <v>0.5</v>
       </c>
       <c r="D44">
-        <v>0.5963880588506598</v>
+        <v>0.59638805885065982</v>
       </c>
       <c r="E44">
-        <v>0.8038303911855553</v>
+        <v>0.80383039118555533</v>
       </c>
       <c r="F44">
-        <v>0.6213770181920134</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <v>0.62137701819201341</v>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -3988,16 +4226,16 @@
         <v>0.5</v>
       </c>
       <c r="D45">
-        <v>0.3712433680005015</v>
+        <v>0.37124336800050151</v>
       </c>
       <c r="E45">
         <v>1.003283588226336</v>
       </c>
       <c r="F45">
-        <v>0.7465312001359479</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+        <v>0.74653120013594787</v>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46" t="s">
         <v>17</v>
       </c>
@@ -4008,16 +4246,19 @@
         <v>0.5</v>
       </c>
       <c r="D46">
-        <v>0.3700663464625333</v>
+        <v>0.37006634646253328</v>
       </c>
       <c r="E46">
         <v>1.004222213919417</v>
       </c>
       <c r="F46">
-        <v>0.7510368500991078</v>
+        <v>0.75103685009910781</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>